--- a/data/dividends_info_20260617.xlsx
+++ b/data/dividends_info_20260617.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>65.25</v>
+        <v>65.16000366210938</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1381215391986467</v>
       </c>
       <c r="J2" t="n">
         <v>271</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.15000152587891</v>
+        <v>65.44999694824219</v>
       </c>
       <c r="I3" t="n">
-        <v>1.07444356654688</v>
+        <v>1.069518766446329</v>
       </c>
       <c r="J3" t="n">
         <v>250</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4600000083446503</v>
       </c>
       <c r="I5" t="n">
-        <v>0.851063831945845</v>
+        <v>0.8695652016169185</v>
       </c>
       <c r="J5" t="n">
         <v>180</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>65.25</v>
+        <v>65.16000366210938</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1381215391986467</v>
       </c>
       <c r="J6" t="n">
         <v>180</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.8700008392334</v>
+        <v>21.82999992370605</v>
       </c>
       <c r="I8" t="n">
-        <v>1.234567853859599</v>
+        <v>1.236830054711986</v>
       </c>
       <c r="J8" t="n">
         <v>159</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4600000083446503</v>
       </c>
       <c r="I11" t="n">
-        <v>0.851063831945845</v>
+        <v>0.8695652016169185</v>
       </c>
       <c r="J11" t="n">
         <v>124</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.900000095367432</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8474576134203634</v>
+        <v>0.8532423013788162</v>
       </c>
       <c r="J12" t="n">
         <v>110</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.8700008392334</v>
+        <v>21.82999992370605</v>
       </c>
       <c r="I14" t="n">
-        <v>1.234567853859599</v>
+        <v>1.236830054711986</v>
       </c>
       <c r="J14" t="n">
         <v>96</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65.25</v>
+        <v>65.16000366210938</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1381215391986467</v>
       </c>
       <c r="J15" t="n">
         <v>96</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.900000095367432</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I16" t="n">
-        <v>5.08474568052218</v>
+        <v>5.172413623006964</v>
       </c>
       <c r="J16" t="n">
         <v>89</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4600000083446503</v>
       </c>
       <c r="I17" t="n">
-        <v>0.851063831945845</v>
+        <v>0.8695652016169185</v>
       </c>
       <c r="J17" t="n">
         <v>68</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.519999980926514</v>
+        <v>5.510000228881836</v>
       </c>
       <c r="I19" t="n">
-        <v>4.528985522895569</v>
+        <v>4.537204893197135</v>
       </c>
       <c r="J19" t="n">
         <v>40</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.170000076293945</v>
+        <v>4.21999979019165</v>
       </c>
       <c r="I20" t="n">
-        <v>3.357314087255939</v>
+        <v>3.317535709963671</v>
       </c>
       <c r="J20" t="n">
         <v>33</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.802000045776367</v>
+        <v>9.883000373840332</v>
       </c>
       <c r="I21" t="n">
-        <v>2.652519881511659</v>
+        <v>2.630780027978177</v>
       </c>
       <c r="J21" t="n">
         <v>33</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.39999961853027</v>
+        <v>14.42000007629395</v>
       </c>
       <c r="I22" t="n">
-        <v>4.166666777045641</v>
+        <v>4.160887634018687</v>
       </c>
       <c r="J22" t="n">
         <v>33</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.721999883651733</v>
+        <v>3.726000070571899</v>
       </c>
       <c r="I23" t="n">
-        <v>5.910800829583942</v>
+        <v>5.904455067984807</v>
       </c>
       <c r="J23" t="n">
         <v>33</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4600000083446503</v>
       </c>
       <c r="I24" t="n">
-        <v>0.851063831945845</v>
+        <v>0.8695652016169185</v>
       </c>
       <c r="J24" t="n">
         <v>33</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.389999866485596</v>
+        <v>6.429999828338623</v>
       </c>
       <c r="I25" t="n">
-        <v>1.564945259615452</v>
+        <v>1.555209994863062</v>
       </c>
       <c r="J25" t="n">
         <v>33</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.54999923706055</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I26" t="n">
-        <v>2.026954261263794</v>
+        <v>2.02150533488478</v>
       </c>
       <c r="J26" t="n">
         <v>33</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.820000171661377</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>2.061855609288493</v>
+        <v>2.058319066387184</v>
       </c>
       <c r="J27" t="n">
         <v>26</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.759999990463257</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="I29" t="n">
-        <v>5.434782627474683</v>
+        <v>5.555555457440915</v>
       </c>
       <c r="J29" t="n">
         <v>26</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.53000020980835</v>
+        <v>4.75</v>
       </c>
       <c r="I31" t="n">
-        <v>1.545253791565751</v>
+        <v>1.473684210526316</v>
       </c>
       <c r="J31" t="n">
         <v>19</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>35.79999923706055</v>
+        <v>35.59999847412109</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4189944223370775</v>
+        <v>0.4213483326664756</v>
       </c>
       <c r="J32" t="n">
         <v>19</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.31999969482422</v>
+        <v>22.5</v>
       </c>
       <c r="I34" t="n">
-        <v>1.120071699902274</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="J34" t="n">
         <v>5</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>30.14999961853027</v>
+        <v>30.04999923706055</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6467661773373704</v>
+        <v>0.6489184856933615</v>
       </c>
       <c r="J35" t="n">
         <v>5</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.46999979019165</v>
+        <v>5.525000095367432</v>
       </c>
       <c r="I37" t="n">
-        <v>5.301645541559323</v>
+        <v>5.248868687679434</v>
       </c>
       <c r="J37" t="n">
         <v>5</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.773999929428101</v>
+        <v>3.799999952316284</v>
       </c>
       <c r="I38" t="n">
-        <v>4.239533730575503</v>
+        <v>4.210526368624617</v>
       </c>
       <c r="J38" t="n">
         <v>5</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.661999940872192</v>
+        <v>2.674000024795532</v>
       </c>
       <c r="I39" t="n">
-        <v>5.206611685896143</v>
+        <v>5.1832460252351</v>
       </c>
       <c r="J39" t="n">
         <v>5</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>52.15999984741211</v>
+        <v>52.31000137329102</v>
       </c>
       <c r="I40" t="n">
-        <v>1.207822089422911</v>
+        <v>1.204358599618909</v>
       </c>
       <c r="J40" t="n">
         <v>5</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.355000019073486</v>
+        <v>6.320000171661377</v>
       </c>
       <c r="I41" t="n">
-        <v>2.202989765221291</v>
+        <v>2.215189813249599</v>
       </c>
       <c r="J41" t="n">
         <v>5</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.95999908447266</v>
+        <v>29.22999954223633</v>
       </c>
       <c r="I43" t="n">
-        <v>2.935082965716461</v>
+        <v>2.907971307942649</v>
       </c>
       <c r="J43" t="n">
         <v>5</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>65.25</v>
+        <v>65.16000366210938</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1381215391986467</v>
       </c>
       <c r="J44" t="n">
         <v>5</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.570000052452087</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6369426538796358</v>
+        <v>0.6289308044070249</v>
       </c>
       <c r="J45" t="n">
         <v>5</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.331999778747559</v>
+        <v>6.400000095367432</v>
       </c>
       <c r="I46" t="n">
-        <v>2.863234465176503</v>
+        <v>2.832812457787805</v>
       </c>
       <c r="J46" t="n">
         <v>5</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.25</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="I47" t="n">
-        <v>2.810810810810811</v>
+        <v>2.819956534380734</v>
       </c>
       <c r="J47" t="n">
         <v>5</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.16499996185303</v>
+        <v>10.26500034332275</v>
       </c>
       <c r="I48" t="n">
-        <v>2.725036901520109</v>
+        <v>2.698489924359183</v>
       </c>
       <c r="J48" t="n">
         <v>5</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.049999952316284</v>
+        <v>1.065000057220459</v>
       </c>
       <c r="I49" t="n">
-        <v>1.285714344102512</v>
+        <v>1.26760556569674</v>
       </c>
       <c r="J49" t="n">
         <v>-2</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.130000114440918</v>
+        <v>3.128000020980835</v>
       </c>
       <c r="I50" t="n">
-        <v>3.514376868310379</v>
+        <v>3.516624017333213</v>
       </c>
       <c r="J50" t="n">
         <v>-2</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.974999904632568</v>
+        <v>2.980000019073486</v>
       </c>
       <c r="I52" t="n">
-        <v>5.378151432907727</v>
+        <v>5.36912748241343</v>
       </c>
       <c r="J52" t="n">
         <v>-9</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.54999923706055</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="I54" t="n">
-        <v>4.029038224098447</v>
+        <v>4.051094946911317</v>
       </c>
       <c r="J54" t="n">
         <v>-13</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9070000052452087</v>
+        <v>0.8939999938011169</v>
       </c>
       <c r="I55" t="n">
-        <v>3.307607478115665</v>
+        <v>3.35570472125461</v>
       </c>
       <c r="J55" t="n">
         <v>-16</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4760000109672546</v>
+        <v>0.4749999940395355</v>
       </c>
       <c r="I56" t="n">
-        <v>4.831932661779336</v>
+        <v>4.842105323918309</v>
       </c>
       <c r="J56" t="n">
         <v>-16</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19.29999923706055</v>
+        <v>19.35000038146973</v>
       </c>
       <c r="I57" t="n">
-        <v>3.108808413048321</v>
+        <v>3.100775132669155</v>
       </c>
       <c r="J57" t="n">
         <v>-16</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.220000267028809</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I58" t="n">
-        <v>2.169197334139026</v>
+        <v>2.173913088547937</v>
       </c>
       <c r="J58" t="n">
         <v>-16</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.410000085830688</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="I59" t="n">
-        <v>7.468879402050181</v>
+        <v>7.499999701976788</v>
       </c>
       <c r="J59" t="n">
         <v>-23</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.25</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I60" t="n">
-        <v>3.636363636363636</v>
+        <v>3.658536670464694</v>
       </c>
       <c r="J60" t="n">
         <v>-23</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>17.09000015258789</v>
+        <v>17.01000022888184</v>
       </c>
       <c r="I61" t="n">
-        <v>1.462843755224561</v>
+        <v>1.469723672169721</v>
       </c>
       <c r="J61" t="n">
         <v>-23</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.070000171661377</v>
+        <v>4.050000190734863</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7371007060118618</v>
+        <v>0.7407407058555365</v>
       </c>
       <c r="J62" t="n">
         <v>-23</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.480000019073486</v>
+        <v>4.5</v>
       </c>
       <c r="I63" t="n">
-        <v>3.348214271459348</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J63" t="n">
         <v>-23</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.5</v>
+        <v>12.75</v>
       </c>
       <c r="I64" t="n">
-        <v>4.64</v>
+        <v>4.549019607843137</v>
       </c>
       <c r="J64" t="n">
         <v>-23</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.233999967575073</v>
+        <v>2.266999959945679</v>
       </c>
       <c r="I65" t="n">
-        <v>4.655326835697686</v>
+        <v>4.587560733900146</v>
       </c>
       <c r="J65" t="n">
         <v>-30</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.27499961853027</v>
+        <v>10.1899995803833</v>
       </c>
       <c r="I66" t="n">
-        <v>2.822384533007714</v>
+        <v>2.845927496977301</v>
       </c>
       <c r="J66" t="n">
         <v>-30</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>42.54000091552734</v>
+        <v>42.5099983215332</v>
       </c>
       <c r="I68" t="n">
-        <v>3.855195027514422</v>
+        <v>3.857915936847419</v>
       </c>
       <c r="J68" t="n">
         <v>-30</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>38.27999877929688</v>
+        <v>38.27000045776367</v>
       </c>
       <c r="I69" t="n">
-        <v>5.224660563682327</v>
+        <v>5.226025545014773</v>
       </c>
       <c r="J69" t="n">
         <v>-30</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.400000095367432</v>
+        <v>3.378000020980835</v>
       </c>
       <c r="I70" t="n">
-        <v>2.94117638809046</v>
+        <v>2.960331538747712</v>
       </c>
       <c r="J70" t="n">
         <v>-30</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>34.83000183105469</v>
+        <v>34.56999969482422</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4262417232135542</v>
+        <v>0.4294475016215498</v>
       </c>
       <c r="J71" t="n">
         <v>-30</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>22.26000022888184</v>
+        <v>22.28000068664551</v>
       </c>
       <c r="I72" t="n">
-        <v>4.132973901798623</v>
+        <v>4.129263786564613</v>
       </c>
       <c r="J72" t="n">
         <v>-30</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>10.94999980926514</v>
+        <v>10.86999988555908</v>
       </c>
       <c r="I73" t="n">
-        <v>2.739726075119751</v>
+        <v>2.759889633472337</v>
       </c>
       <c r="J73" t="n">
         <v>-30</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>87.12000274658203</v>
+        <v>86.77999877929688</v>
       </c>
       <c r="I74" t="n">
-        <v>1.193755701575437</v>
+        <v>1.198432835479727</v>
       </c>
       <c r="J74" t="n">
         <v>-30</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>47.59000015258789</v>
+        <v>48</v>
       </c>
       <c r="I75" t="n">
-        <v>1.470897242604726</v>
+        <v>1.458333333333333</v>
       </c>
       <c r="J75" t="n">
         <v>-30</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>65.05000305175781</v>
+        <v>65.44999694824219</v>
       </c>
       <c r="I76" t="n">
-        <v>3.382013676847246</v>
+        <v>3.361344694545607</v>
       </c>
       <c r="J76" t="n">
         <v>-30</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>10.92000007629395</v>
+        <v>10.95400047302246</v>
       </c>
       <c r="I77" t="n">
-        <v>7.875457820435004</v>
+        <v>7.851012989437148</v>
       </c>
       <c r="J77" t="n">
         <v>-30</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>13.78400039672852</v>
+        <v>13.76200008392334</v>
       </c>
       <c r="I78" t="n">
-        <v>4.062681252772672</v>
+        <v>4.069175967047026</v>
       </c>
       <c r="J78" t="n">
         <v>-30</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>10.18000030517578</v>
+        <v>10.34000015258789</v>
       </c>
       <c r="I80" t="n">
-        <v>2.946954725015794</v>
+        <v>2.901353922368329</v>
       </c>
       <c r="J80" t="n">
         <v>-30</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>93.30000305175781</v>
+        <v>92.59999847412109</v>
       </c>
       <c r="I82" t="n">
-        <v>2.207931331853465</v>
+        <v>2.22462206689529</v>
       </c>
       <c r="J82" t="n">
         <v>-30</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>16.79000091552734</v>
+        <v>16.73999977111816</v>
       </c>
       <c r="I83" t="n">
-        <v>4.466944366312704</v>
+        <v>4.480286799609097</v>
       </c>
       <c r="J83" t="n">
         <v>-30</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>15.81999969482422</v>
+        <v>15.77999973297119</v>
       </c>
       <c r="I84" t="n">
-        <v>1.89633379132207</v>
+        <v>1.901140716581707</v>
       </c>
       <c r="J84" t="n">
         <v>-30</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>49.70000076293945</v>
+        <v>50.40000152587891</v>
       </c>
       <c r="I85" t="n">
-        <v>1.710261543162455</v>
+        <v>1.686507885448278</v>
       </c>
       <c r="J85" t="n">
         <v>-30</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>38.31999969482422</v>
+        <v>37.88000106811523</v>
       </c>
       <c r="I86" t="n">
-        <v>2.218162856913611</v>
+        <v>2.243928131024978</v>
       </c>
       <c r="J86" t="n">
         <v>-30</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>64.81999969482422</v>
+        <v>64.55999755859375</v>
       </c>
       <c r="I87" t="n">
-        <v>2.00555385084922</v>
+        <v>2.013630807250478</v>
       </c>
       <c r="J87" t="n">
         <v>-30</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>7.28000020980835</v>
+        <v>7.440000057220459</v>
       </c>
       <c r="I88" t="n">
-        <v>8.241758004232192</v>
+        <v>8.064516067008695</v>
       </c>
       <c r="J88" t="n">
         <v>-30</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>6.900000095367432</v>
+        <v>6.75</v>
       </c>
       <c r="I89" t="n">
-        <v>6.81159410875301</v>
+        <v>6.962962962962963</v>
       </c>
       <c r="J89" t="n">
         <v>-30</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>5</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I92" t="n">
-        <v>4.3</v>
+        <v>4.308617432097048</v>
       </c>
       <c r="J92" t="n">
         <v>-30</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>21.8700008392334</v>
+        <v>21.82999992370605</v>
       </c>
       <c r="I93" t="n">
-        <v>1.234567853859599</v>
+        <v>1.236830054711986</v>
       </c>
       <c r="J93" t="n">
         <v>-30</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>9.659999847412109</v>
+        <v>9.739999771118164</v>
       </c>
       <c r="I94" t="n">
-        <v>2.07039340744482</v>
+        <v>2.053388138601976</v>
       </c>
       <c r="J94" t="n">
         <v>-30</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>9.185000419616699</v>
+        <v>9.069999694824219</v>
       </c>
       <c r="I95" t="n">
-        <v>2.612955786996202</v>
+        <v>2.646086086827055</v>
       </c>
       <c r="J95" t="n">
         <v>-30</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>22.81999969482422</v>
+        <v>22.96999931335449</v>
       </c>
       <c r="I96" t="n">
-        <v>3.461875594061375</v>
+        <v>3.439268714042595</v>
       </c>
       <c r="J96" t="n">
         <v>-30</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.260000228881836</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="I97" t="n">
-        <v>1.768060759567112</v>
+        <v>1.761363566373337</v>
       </c>
       <c r="J97" t="n">
         <v>-30</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.534999847412109</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="I100" t="n">
-        <v>8.482020090933979</v>
+        <v>8.488514275503649</v>
       </c>
       <c r="J100" t="n">
         <v>-30</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.309999942779541</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I101" t="n">
-        <v>2.597402661742239</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J101" t="n">
         <v>-30</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>13.60000038146973</v>
+        <v>13.30000019073486</v>
       </c>
       <c r="I102" t="n">
-        <v>1.47058819404523</v>
+        <v>1.503759376930877</v>
       </c>
       <c r="J102" t="n">
         <v>-30</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.275000095367432</v>
+        <v>7.264999866485596</v>
       </c>
       <c r="I103" t="n">
-        <v>1.415807541577742</v>
+        <v>1.417756392194205</v>
       </c>
       <c r="J103" t="n">
         <v>-30</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>6.064000129699707</v>
+        <v>6.110000133514404</v>
       </c>
       <c r="I104" t="n">
-        <v>3.133245315570416</v>
+        <v>3.109656233194125</v>
       </c>
       <c r="J104" t="n">
         <v>-30</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>10.44499969482422</v>
+        <v>10.60499954223633</v>
       </c>
       <c r="I105" t="n">
-        <v>4.135950336255805</v>
+        <v>4.073550387998432</v>
       </c>
       <c r="J105" t="n">
         <v>-30</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>26.45999908447266</v>
+        <v>26.19000053405762</v>
       </c>
       <c r="I106" t="n">
-        <v>1.66288743470971</v>
+        <v>1.680030511751314</v>
       </c>
       <c r="J106" t="n">
         <v>-30</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>6.800000190734863</v>
+        <v>6.710000038146973</v>
       </c>
       <c r="I108" t="n">
-        <v>6.911764512012579</v>
+        <v>7.004470899076101</v>
       </c>
       <c r="J108" t="n">
         <v>-30</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>54.13999938964844</v>
+        <v>53.61999893188477</v>
       </c>
       <c r="I109" t="n">
-        <v>2.585888466536776</v>
+        <v>2.610966109451933</v>
       </c>
       <c r="J109" t="n">
         <v>-30</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.565000057220459</v>
+        <v>3.543999910354614</v>
       </c>
       <c r="I110" t="n">
-        <v>8.415147130008812</v>
+        <v>8.465011500803957</v>
       </c>
       <c r="J110" t="n">
         <v>-30</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>15.85000038146973</v>
+        <v>16</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7570977735766636</v>
+        <v>0.75</v>
       </c>
       <c r="J111" t="n">
         <v>-30</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>22.79999923706055</v>
+        <v>23.04999923706055</v>
       </c>
       <c r="I113" t="n">
-        <v>3.070175541331493</v>
+        <v>3.036876456266935</v>
       </c>
       <c r="J113" t="n">
         <v>-30</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.700000047683716</v>
+        <v>2.799999952316284</v>
       </c>
       <c r="I114" t="n">
-        <v>1.29629627340288</v>
+        <v>1.250000021287374</v>
       </c>
       <c r="J114" t="n">
         <v>-30</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.409999847412109</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="I115" t="n">
-        <v>6.099815329160435</v>
+        <v>6.077348258424673</v>
       </c>
       <c r="J115" t="n">
         <v>-30</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.9290000200271606</v>
+        <v>0.9359999895095825</v>
       </c>
       <c r="I116" t="n">
-        <v>7.534983691168645</v>
+        <v>7.478632562450832</v>
       </c>
       <c r="J116" t="n">
         <v>-30</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>50.54999923706055</v>
+        <v>50.65000152587891</v>
       </c>
       <c r="I117" t="n">
-        <v>1.404549971742563</v>
+        <v>1.401776858066303</v>
       </c>
       <c r="J117" t="n">
         <v>-30</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>100.6999969482422</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="I118" t="n">
-        <v>1.340615730796768</v>
+        <v>1.34462149350867</v>
       </c>
       <c r="J118" t="n">
         <v>-30</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>7.699999809265137</v>
+        <v>7.659999847412109</v>
       </c>
       <c r="I119" t="n">
-        <v>1.038961064696896</v>
+        <v>1.044386443780773</v>
       </c>
       <c r="J119" t="n">
         <v>-30</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.699999809265137</v>
+        <v>4.730000019073486</v>
       </c>
       <c r="I121" t="n">
-        <v>3.617021423381296</v>
+        <v>3.594080323773437</v>
       </c>
       <c r="J121" t="n">
         <v>-30</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>7.400000095367432</v>
+        <v>7.5</v>
       </c>
       <c r="I122" t="n">
-        <v>4.013513461789396</v>
+        <v>3.96</v>
       </c>
       <c r="J122" t="n">
         <v>-30</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>60</v>
+        <v>60.29999923706055</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7500000000000001</v>
+        <v>0.7462686661585043</v>
       </c>
       <c r="J123" t="n">
         <v>-30</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5.820000171661377</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6872852030961643</v>
+        <v>0.7067137999710191</v>
       </c>
       <c r="J124" t="n">
         <v>-30</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>38.34000015258789</v>
+        <v>37.97999954223633</v>
       </c>
       <c r="I125" t="n">
-        <v>2.738654136205387</v>
+        <v>2.76461298750762</v>
       </c>
       <c r="J125" t="n">
         <v>-30</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>16.97999954223633</v>
+        <v>17.03000068664551</v>
       </c>
       <c r="I127" t="n">
-        <v>2.237927033241561</v>
+        <v>2.231356339861961</v>
       </c>
       <c r="J127" t="n">
         <v>-30</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>26.14999961853027</v>
+        <v>25.84000015258789</v>
       </c>
       <c r="I128" t="n">
-        <v>2.294455100392549</v>
+        <v>2.321981410437064</v>
       </c>
       <c r="J128" t="n">
         <v>-30</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>36.45000076293945</v>
+        <v>36.20000076293945</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9602194586395252</v>
+        <v>0.9668508083522478</v>
       </c>
       <c r="J129" t="n">
         <v>-30</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>3.105000019073486</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="I131" t="n">
-        <v>0.322061189648042</v>
+        <v>0.3496503624754485</v>
       </c>
       <c r="J131" t="n">
         <v>-30</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>24.56999969482422</v>
+        <v>24.39999961853027</v>
       </c>
       <c r="I132" t="n">
-        <v>4.558404615022983</v>
+        <v>4.590164006188878</v>
       </c>
       <c r="J132" t="n">
         <v>-30</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.364000082015991</v>
+        <v>2.328000068664551</v>
       </c>
       <c r="I135" t="n">
-        <v>3.904399187722855</v>
+        <v>3.964776515360997</v>
       </c>
       <c r="J135" t="n">
         <v>-30</v>
@@ -8592,78 +8592,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PIQUADRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>